--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -1,146 +1,415 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\tgh-jde-download\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AFF65F-3640-4211-8510-14CF31BF1467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="1605" windowWidth="16815" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="14055" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="JDE配置" sheetId="1" r:id="rId1"/>
-    <sheet name="房产税配置" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JDE配置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房产税配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="登录配置" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t>配置项</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>jde_url</t>
-  </si>
-  <si>
-    <t>https://sphkjdewcn04.hk.swireproperties.com:8130/jde/E1Menu.maf?jdeowpBackButtonProtect=PROTECTED</t>
-  </si>
-  <si>
-    <t>必填；可由 JDE_URL 环境变量覆盖</t>
-  </si>
-  <si>
-    <t>jde_credential_name</t>
-  </si>
-  <si>
-    <t>Windows 通用凭据名称；必填，读取其中的用户名和密码</t>
-  </si>
-  <si>
-    <t>jde_environment</t>
-  </si>
-  <si>
-    <t>JPD920</t>
-  </si>
-  <si>
-    <t>可由 JDE_ENVIRONMENT 环境变量覆盖</t>
-  </si>
-  <si>
-    <t>jde_role</t>
-  </si>
-  <si>
-    <t>可由 JDE_ROLE 环境变量覆盖</t>
-  </si>
-  <si>
-    <t>headless</t>
-  </si>
-  <si>
-    <t>false 显示浏览器；true 无界面运行</t>
-  </si>
-  <si>
-    <t>JDE</t>
-  </si>
-  <si>
-    <t>*ALL</t>
-  </si>
-  <si>
-    <t>明细账分类帐类型</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>明细账自公司</t>
-  </si>
-  <si>
-    <t>02501</t>
-  </si>
-  <si>
-    <t>明细账至公司</t>
-  </si>
-  <si>
-    <t>02504</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="25">
+    <font>
       <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color rgb="FF244438"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <charset val="134"/>
       <color rgb="FF244438"/>
-      <name val="Microsoft YaHei"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="36">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCEE8D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0F8F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEE8D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -163,69 +432,396 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment vertical="center" wrapText="1"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,87 +1013,122 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFA8D5B5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col width="25" customWidth="1" style="1" min="1" max="1"/>
+    <col width="65" customWidth="1" style="1" min="2" max="2"/>
+    <col width="60" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
+    <row r="1" ht="33.95" customHeight="1" s="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>配置项</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
+    <row r="2" ht="39.95" customHeight="1" s="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>jde_url</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>https://sphkjdewcn04.hk.swireproperties.com:8130/jde/E1Menu.maf?jdeowpBackButtonProtect=PROTECTED</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>必填；可由 JDE_URL 环境变量覆盖</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
+    <row r="3" ht="39.95" customHeight="1" s="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>jde_credential_name</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>JDE</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Windows 通用凭据名称；必填，读取其中的用户名和密码</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
+    <row r="4" ht="39.95" customHeight="1" s="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>jde_environment</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>JPD920</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>可由 JDE_ENVIRONMENT 环境变量覆盖</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
+    <row r="5" ht="39.95" customHeight="1" s="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>jde_role</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>*ALL</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>可由 JDE_ROLE 环境变量覆盖</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
+    <row r="6" ht="39.95" customHeight="1" s="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
       </c>
       <c r="B6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>false 显示浏览器；true 无界面运行</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -506,57 +1137,110 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B66B0E5-39BB-4F4C-98EF-C4E06681F117}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="22.5" customWidth="1"/>
-    <col min="2" max="2" width="44.875" customWidth="1"/>
+    <col width="22.5" customWidth="1" style="1" min="1" max="1"/>
+    <col width="44.875" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
+    <row r="1" ht="15" customHeight="1" s="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>配置项</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
+    <row r="2" ht="16.5" customHeight="1" s="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>明细账分类帐类型</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>20</v>
+    <row r="3" ht="16.5" customHeight="1" s="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>明细账自公司</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>02501</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
+    <row r="4" ht="16.5" customHeight="1" s="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>明细账至公司</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>02504</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
+    <row r="5" ht="16.5" customHeight="1" s="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>会计期间</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{a3ecabac-5b6e-420d-b686-5fca49014776}" enabled="1" method="Privileged" siteId="{ae326a90-5548-4db0-a52c-9b8e317c2010}" contentBits="0" removed="0"/>
-</clbl:labelList>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col width="20" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" customWidth="1" style="1" min="2" max="3"/>
+    <col width="70" customWidth="1" style="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>window凭据</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>凭据账号</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>共享盘路径</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -9,6 +9,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JDE配置" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房产税配置" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="登录配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WechatRobot1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WechatRobot2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1243,4 +1245,100 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="1" min="1" max="1"/>
+    <col width="70" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>配置项</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>webhook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>企业微信机器人 Webhook 地址；留空跳过通知</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="1" min="1" max="1"/>
+    <col width="70" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>配置项</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>webhook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>企业微信机器人 Webhook 地址；留空跳过通知</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>